--- a/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4170B3-5965-4EBB-842C-87D1D7E103D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C552353-096E-4C09-8591-CEA7B7E2E0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -79,10 +82,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Posture</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>血量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -103,7 +102,35 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>架势，平衡值</t>
+    <t>HpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>血上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔力上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpMax</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力上限</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -512,7 +539,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
@@ -527,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -539,7 +566,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -550,7 +577,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -561,36 +588,52 @@
         <v>14</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="1">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="B11" s="2">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B12" s="2">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>

--- a/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/#exgas.attribute.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C552353-096E-4C09-8591-CEA7B7E2E0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24D4D40-2E5F-418B-B7B8-4A3E4A14FC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -36,12 +36,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -131,6 +125,18 @@
   </si>
   <si>
     <t>耐力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -487,45 +493,45 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
@@ -536,10 +542,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
@@ -551,10 +557,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -563,10 +569,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -574,10 +580,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -585,10 +591,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -596,10 +602,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -607,10 +613,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -618,10 +624,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -629,10 +635,10 @@
         <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
